--- a/data/availability/projects/city-edge-developments/mazarine-hub-new-alamein.xlsx
+++ b/data/availability/projects/city-edge-developments/mazarine-hub-new-alamein.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mazarine-hub-new-alamein</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -709,7 +719,6 @@
       <c r="G2" t="n">
         <v>75</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -720,7 +729,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -766,7 +775,6 @@
       <c r="G3" t="n">
         <v>85</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -777,7 +785,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -823,7 +831,6 @@
       <c r="G4" t="n">
         <v>90</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -834,7 +841,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -880,7 +887,6 @@
       <c r="G5" t="n">
         <v>110</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -891,7 +897,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -937,7 +943,6 @@
       <c r="G6" t="n">
         <v>140</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -948,7 +953,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -994,7 +999,6 @@
       <c r="G7" t="n">
         <v>170</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1005,7 +1009,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
